--- a/feedback_forms/003_risk_communication_awareness_survey--feedback_forms.xlsx
+++ b/feedback_forms/003_risk_communication_awareness_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>risk_communication_channels_2</t>
+          <t>communication_channels_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>risk_communication_policies_2</t>
+          <t>participant_understanding_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Risk Communication Policies 2</t>
+          <t>Participant Understanding 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -783,305 +783,6 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>participant_understanding_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Participant Understanding 2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>organization_communication_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Organization Communication 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>participant_feedback_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Participant Feedback 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>communication_channels_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Communication Channels</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>risk_factors_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Risk Factors 3</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>participant_understanding_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Participant Understanding 3</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>risk_communication_policies_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Risk Communication Policies 3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>communication_efforts_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Communication Efforts 3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>participant_feedback_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Participant Feedback 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>communication_channels_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Communication Channels</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>risk_factors_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Risk Factors 4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_understanding_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Participant Understanding</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_feedback_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Participant Feedback</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1136,7 +837,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>Risk Communication Channels</t>
         </is>
       </c>
     </row>
@@ -1148,199 +849,199 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>risk_communication_policies_choices</t>
+          <t>communication_efforts_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>risk_communication_policies_choices</t>
+          <t>communication_efforts_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>risk_communication_channels_2_choices</t>
+          <t>communication_efforts_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>risk_communication_channels_2_choices</t>
+          <t>risk_communication_policies_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>risk_communication_channels_2_choices</t>
+          <t>risk_communication_policies_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>risk_communication_channels</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>risk_factors_2_choices</t>
+          <t>communication_channels_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>risk_factors</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>risk_factors</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>risk_factors_2_choices</t>
+          <t>communication_channels_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>risk_factors</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>risk_factors</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>risk_factors_2_choices</t>
+          <t>communication_channels_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>risk_factors</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>risk_factors</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>risk_communication_policies_2_choices</t>
+          <t>participant_understanding_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>risk_communication_policies_2_choices</t>
+          <t>participant_understanding_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>Unclear</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>risk_communication_policies_2_choices</t>
+          <t>communication_efforts_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>risk_communication_policies</t>
+          <t>Frequent</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>risk_communication_efforts</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>risk_communication_efforts</t>
+          <t>Occasional</t>
         </is>
       </c>
     </row>
@@ -1369,437 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>risk_communication_efforts</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>risk_communication_efforts</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>communication_efforts_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>risk_communication_efforts</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>risk_communication_efforts</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>participant_understanding_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>participant_understanding_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>participant_understanding_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>organization_communication_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>organization_communication</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>organization_communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>organization_communication_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>organization_communication</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>organization_communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>organization_communication_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>organization_communication</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>organization_communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>communication_channels_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>risk_communication_channels</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>risk_communication_channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>communication_channels_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>risk_communication_channels</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>risk_communication_channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>communication_channels_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>risk_communication_channels</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>risk_communication_channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>participant_understanding_3_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>participant_understanding_3_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>participant_understanding_3_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>risk_communication_policies_3_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>risk_communication_policies</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>risk_communication_policies</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>risk_communication_policies_3_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>risk_communication_policies</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>risk_communication_policies</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>risk_communication_policies_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>risk_communication_policies</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>risk_communication_policies</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>communication_efforts_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>communication_efforts</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>communication_efforts</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>communication_efforts_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>communication_efforts</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>communication_efforts</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>communication_efforts_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>communication_efforts</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>communication_efforts</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>communication_channels_3_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>communication_channels</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>communication_channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>communication_channels_3_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>communication_channels</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>communication_channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>communication_channels_3_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>communication_channels</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>communication_channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>participant_understanding_4_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>participant_understanding_4_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>participant_understanding_4_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>participant_understanding</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
